--- a/inventory_tracker.xlsx
+++ b/inventory_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fds44370/skills/inventory_tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D967AF-EDFD-3147-A5C7-073BEB8EB755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD50490-1F76-4042-B725-146BE1A89174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="17680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,12 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>Inventory Dashboard</t>
   </si>
   <si>
-    <t>Type product names in the yellow column (A). Everything else is calculated from the Purchases and Sales sheets. Names must match exactly.</t>
+    <t>Type product names once in the yellow list in column P. Everything else is calculated from the Purchases and Sales sheets. Names must match exactly.</t>
   </si>
   <si>
     <t>Period options</t>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>Yesterday</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>All items</t>
   </si>
   <si>
     <t>Last 7 days</t>
@@ -134,22 +140,28 @@
     <t>This month</t>
   </si>
   <si>
-    <t>Widget</t>
+    <t>Product list (type here)</t>
+  </si>
+  <si>
+    <t>Item options</t>
   </si>
   <si>
     <t>Last month</t>
   </si>
   <si>
-    <t>Gadget</t>
+    <t>Widget</t>
   </si>
   <si>
     <t>This year</t>
   </si>
   <si>
-    <t>Gizmo</t>
+    <t>Gadget</t>
   </si>
   <si>
     <t>Custom range</t>
+  </si>
+  <si>
+    <t>Gizmo</t>
   </si>
   <si>
     <t>Date of Purchase</t>
@@ -293,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,6 +325,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -430,13 +444,13 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -479,7 +493,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8A4D-1243-8A79-D8A6ABB04547}"/>
+              <c16:uniqueId val="{00000000-E64B-804A-A776-C7E671D64641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -527,13 +541,13 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>70</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -576,7 +590,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8A4D-1243-8A79-D8A6ABB04547}"/>
+              <c16:uniqueId val="{00000001-E64B-804A-A776-C7E671D64641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -737,13 +751,13 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -786,7 +800,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-067F-3F4F-98D8-8D58BDF31DFC}"/>
+              <c16:uniqueId val="{00000000-CE2E-A846-ADAB-863657F773B1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -947,13 +961,13 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>450</c:v>
+                  <c:v>738</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -996,7 +1010,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3159-7C4D-845E-B93E87AFE2DB}"/>
+              <c16:uniqueId val="{00000000-0FC2-5942-8DE9-1C4EEF0432EE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1044,13 +1058,13 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>490</c:v>
+                  <c:v>780</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>370</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>390</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1093,7 +1107,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3159-7C4D-845E-B93E87AFE2DB}"/>
+              <c16:uniqueId val="{00000001-0FC2-5942-8DE9-1C4EEF0432EE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1254,13 +1268,13 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>175</c:v>
+                  <c:v>272.625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1303,7 +1317,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-80AF-094D-8897-A5097DBD13EB}"/>
+              <c16:uniqueId val="{00000000-EBB3-8A46-A4EB-C4D29F8DCEEF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1813,24 +1827,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3">
         <v>46266</v>
@@ -1847,25 +1861,58 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46268</v>
+      </c>
+      <c r="C3" s="2">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46270</v>
+      </c>
+      <c r="C4" s="2">
+        <v>200</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46285</v>
+      </c>
+      <c r="C5" s="2">
+        <v>60</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>288</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
@@ -11433,7 +11480,7 @@
       <c r="C962" s="2"/>
       <c r="D962" s="4"/>
       <c r="E962" s="5" t="str">
-        <f t="shared" ref="E962:E1001" si="15">IF(OR(C962="",D962=""),"",C962*D962)</f>
+        <f t="shared" ref="E962:E1025" si="15">IF(OR(C962="",D962=""),"",C962*D962)</f>
         <v/>
       </c>
     </row>
@@ -11841,9 +11888,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown product" error="Add the product to the Dashboard product list first." xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown product" error="Add the product to the Dashboard product list (column P) first." xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>Dashboard!$A$9:$A$38</xm:f>
+            <xm:f>Dashboard!$P$9:$P$38</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A1001</xm:sqref>
         </x14:dataValidation>
@@ -11866,24 +11913,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3">
         <v>46275</v>
@@ -11900,25 +11947,58 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46277</v>
+      </c>
+      <c r="C3" s="2">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4">
+        <v>18.5</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46280</v>
+      </c>
+      <c r="C4" s="2">
+        <v>120</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3.25</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>390</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46290</v>
+      </c>
+      <c r="C5" s="2">
+        <v>40</v>
+      </c>
+      <c r="D5" s="4">
+        <v>7.25</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>290</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
@@ -21486,7 +21566,7 @@
       <c r="C962" s="2"/>
       <c r="D962" s="4"/>
       <c r="E962" s="5" t="str">
-        <f t="shared" ref="E962:E1001" si="15">IF(OR(C962="",D962=""),"",C962*D962)</f>
+        <f t="shared" ref="E962:E1025" si="15">IF(OR(C962="",D962=""),"",C962*D962)</f>
         <v/>
       </c>
     </row>
@@ -21894,9 +21974,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown product" error="Add the product to the Dashboard product list first." xr:uid="{00000000-0002-0000-0100-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown product" error="Add the product to the Dashboard product list (column P) first." xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>Dashboard!$A$9:$A$38</xm:f>
+            <xm:f>Dashboard!$P$9:$P$38</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A1001</xm:sqref>
         </x14:dataValidation>
@@ -21908,20 +21988,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="12" width="14" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -21929,18 +22011,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -21956,20 +22038,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="13">
         <f ca="1">CHOOSE(MATCH($B$3,$N$3:$N$11,0),0,TODAY(),TODAY()-1,TODAY()-6,TODAY()-29,DATE(YEAR(TODAY()),MONTH(TODAY()),1),DATE(YEAR(TODAY()),MONTH(TODAY())-1,1),DATE(YEAR(TODAY()),1,1),IF($B$4="",0,$B$4))</f>
-        <v>46023</v>
+        <v>0</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="13">
         <f ca="1">CHOOSE(MATCH($B$3,$N$3:$N$11,0),2958465,TODAY(),TODAY()-1,TODAY(),TODAY(),TODAY(),EOMONTH(TODAY(),-1),TODAY(),IF($D$4="",2958465,$D$4))</f>
-        <v>46305</v>
+        <v>2958465</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>11</v>
@@ -21985,252 +22067,290 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="N6" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="15">
         <f ca="1">SUM(F9:F38)</f>
-        <v>450</v>
+        <v>1688</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7" s="15">
         <f ca="1">SUM(G9:G38)</f>
-        <v>490</v>
+        <v>1540</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" s="15">
         <f ca="1">SUM(J9:J38)</f>
-        <v>175</v>
+        <v>582.625</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7" s="16">
         <f ca="1">IF(D7=0,"",F7/D7)</f>
-        <v>0.35714285714285715</v>
+        <v>0.3783279220779221</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="17">
+        <v>32</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="str">
+        <f t="shared" ref="A9:A38" si="0">IF($B$6="All items",IF($P9="","",$P9),IF(ROW()=9,$B$6,""))</f>
+        <v>Widget</v>
+      </c>
+      <c r="B9" s="19">
         <f ca="1">IF($A9="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A9,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>100</v>
-      </c>
-      <c r="C9" s="17">
+        <v>160</v>
+      </c>
+      <c r="C9" s="19">
         <f ca="1">IF($A9="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A9,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>70</v>
-      </c>
-      <c r="D9" s="17">
+        <v>110</v>
+      </c>
+      <c r="D9" s="19">
         <f>IF($A9="","",SUMIF(Purchases!$A$2:$A$1001,$A9,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A9,Sales!$C$2:$C$1001))</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E9" s="5">
         <f>IF($A9="","",IF(SUMIF(Purchases!$A$2:$A$1001,$A9,Purchases!$C$2:$C$1001)=0,0,SUMIF(Purchases!$A$2:$A$1001,$A9,Purchases!$E$2:$E$1001)/SUMIF(Purchases!$A$2:$A$1001,$A9,Purchases!$C$2:$C$1001)))</f>
-        <v>4.5</v>
+        <v>4.6124999999999998</v>
       </c>
       <c r="F9" s="5">
         <f ca="1">IF($A9="","",SUMIFS(Purchases!$E$2:$E$1001,Purchases!$A$2:$A$1001,$A9,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>450</v>
+        <v>738</v>
       </c>
       <c r="G9" s="5">
         <f ca="1">IF($A9="","",SUMIFS(Sales!$E$2:$E$1001,Sales!$A$2:$A$1001,$A9,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>490</v>
+        <v>780</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" ref="H9:H38" ca="1" si="0">IF($A9="","",IF(C9=0,0,G9/C9))</f>
-        <v>7</v>
+        <f t="shared" ref="H9:H38" ca="1" si="1">IF($A9="","",IF(C9=0,0,G9/C9))</f>
+        <v>7.0909090909090908</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" ref="I9:I38" ca="1" si="1">IF($A9="","",C9*E9)</f>
-        <v>315</v>
+        <f t="shared" ref="I9:I38" ca="1" si="2">IF($A9="","",C9*E9)</f>
+        <v>507.375</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J38" ca="1" si="2">IF($A9="","",G9-I9)</f>
-        <v>175</v>
-      </c>
-      <c r="K9" s="18">
-        <f t="shared" ref="K9:K38" ca="1" si="3">IF($A9="","",IF(G9=0,0,J9/G9))</f>
-        <v>0.35714285714285715</v>
-      </c>
-      <c r="L9" s="19">
-        <f t="shared" ref="L9:L38" ca="1" si="4">IF($A9="","",IF(C9=0,"No sales",IF(D9&lt;=0,0,ROUND(D9/(C9/$F$5),1))))</f>
-        <v>17.100000000000001</v>
+        <f t="shared" ref="J9:J38" ca="1" si="3">IF($A9="","",G9-I9)</f>
+        <v>272.625</v>
+      </c>
+      <c r="K9" s="20">
+        <f t="shared" ref="K9:K38" ca="1" si="4">IF($A9="","",IF(G9=0,0,J9/G9))</f>
+        <v>0.34951923076923075</v>
+      </c>
+      <c r="L9" s="21">
+        <f t="shared" ref="L9:L38" ca="1" si="5">IF($A9="","",IF(C9=0,"No sales",IF(D9&lt;=0,0,ROUND(D9/(C9/$F$5),1))))</f>
+        <v>18.2</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="17">
+        <v>35</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>Gadget</v>
+      </c>
+      <c r="B10" s="19">
         <f ca="1">IF($A10="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A10,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="17">
+        <v>50</v>
+      </c>
+      <c r="C10" s="19">
         <f ca="1">IF($A10="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A10,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="17">
+        <v>20</v>
+      </c>
+      <c r="D10" s="19">
         <f>IF($A10="","",SUMIF(Purchases!$A$2:$A$1001,$A10,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A10,Sales!$C$2:$C$1001))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E10" s="5">
         <f>IF($A10="","",IF(SUMIF(Purchases!$A$2:$A$1001,$A10,Purchases!$C$2:$C$1001)=0,0,SUMIF(Purchases!$A$2:$A$1001,$A10,Purchases!$E$2:$E$1001)/SUMIF(Purchases!$A$2:$A$1001,$A10,Purchases!$C$2:$C$1001)))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">IF($A10="","",SUMIFS(Purchases!$E$2:$E$1001,Purchases!$A$2:$A$1001,$A10,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G10" s="5">
         <f ca="1">IF($A10="","",SUMIFS(Sales!$E$2:$E$1001,Sales!$A$2:$A$1001,$A10,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="H10" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>18.5</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>240</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="18">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="19" t="str">
+        <v>130</v>
+      </c>
+      <c r="K10" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>No sales</v>
+        <v>0.35135135135135137</v>
+      </c>
+      <c r="L10" s="21">
+        <f t="shared" ca="1" si="5"/>
+        <v>60</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="17">
+        <v>37</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" ref="Q10:Q39" si="6">IF($P9="","",$P9)</f>
+        <v>Widget</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>Gizmo</v>
+      </c>
+      <c r="B11" s="19">
         <f ca="1">IF($A11="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A11,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="17">
+        <v>200</v>
+      </c>
+      <c r="C11" s="19">
         <f ca="1">IF($A11="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A11,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="17">
+        <v>120</v>
+      </c>
+      <c r="D11" s="19">
         <f>IF($A11="","",SUMIF(Purchases!$A$2:$A$1001,$A11,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A11,Sales!$C$2:$C$1001))</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E11" s="5">
         <f>IF($A11="","",IF(SUMIF(Purchases!$A$2:$A$1001,$A11,Purchases!$C$2:$C$1001)=0,0,SUMIF(Purchases!$A$2:$A$1001,$A11,Purchases!$E$2:$E$1001)/SUMIF(Purchases!$A$2:$A$1001,$A11,Purchases!$C$2:$C$1001)))</f>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="F11" s="5">
         <f ca="1">IF($A11="","",SUMIFS(Purchases!$E$2:$E$1001,Purchases!$A$2:$A$1001,$A11,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G11" s="5">
         <f ca="1">IF($A11="","",SUMIFS(Sales!$E$2:$E$1001,Sales!$A$2:$A$1001,$A11,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="H11" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>3.25</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>210</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="18">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="19" t="str">
+        <v>180</v>
+      </c>
+      <c r="K11" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>No sales</v>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="L11" s="21">
+        <f t="shared" ca="1" si="5"/>
+        <v>26.7</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="17" t="str">
+        <v>39</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="6"/>
+        <v>Gadget</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B12" s="19" t="str">
         <f>IF($A12="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A12,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C12" s="17" t="str">
+      <c r="C12" s="19" t="str">
         <f>IF($A12="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A12,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D12" s="17" t="str">
+      <c r="D12" s="19" t="str">
         <f>IF($A12="","",SUMIF(Purchases!$A$2:$A$1001,$A12,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A12,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22247,37 +22367,45 @@
         <v/>
       </c>
       <c r="H12" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I12" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J12" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K12" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L12" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" t="str">
+        <f t="shared" si="6"/>
+        <v>Gizmo</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I12" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J12" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K12" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L12" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="17" t="str">
+      <c r="B13" s="19" t="str">
         <f>IF($A13="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A13,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C13" s="17" t="str">
+      <c r="C13" s="19" t="str">
         <f>IF($A13="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A13,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D13" s="17" t="str">
+      <c r="D13" s="19" t="str">
         <f>IF($A13="","",SUMIF(Purchases!$A$2:$A$1001,$A13,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A13,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22294,37 +22422,45 @@
         <v/>
       </c>
       <c r="H13" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J13" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K13" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L13" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I13" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J13" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K13" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L13" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="17" t="str">
+      <c r="B14" s="19" t="str">
         <f>IF($A14="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A14,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C14" s="17" t="str">
+      <c r="C14" s="19" t="str">
         <f>IF($A14="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A14,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D14" s="17" t="str">
+      <c r="D14" s="19" t="str">
         <f>IF($A14="","",SUMIF(Purchases!$A$2:$A$1001,$A14,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A14,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22341,37 +22477,45 @@
         <v/>
       </c>
       <c r="H14" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I14" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J14" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K14" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L14" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I14" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J14" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K14" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L14" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="17" t="str">
+      <c r="B15" s="19" t="str">
         <f>IF($A15="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A15,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C15" s="17" t="str">
+      <c r="C15" s="19" t="str">
         <f>IF($A15="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A15,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D15" s="17" t="str">
+      <c r="D15" s="19" t="str">
         <f>IF($A15="","",SUMIF(Purchases!$A$2:$A$1001,$A15,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A15,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22388,37 +22532,45 @@
         <v/>
       </c>
       <c r="H15" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I15" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J15" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K15" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L15" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I15" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J15" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K15" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L15" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="17" t="str">
+      <c r="B16" s="19" t="str">
         <f>IF($A16="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A16,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C16" s="17" t="str">
+      <c r="C16" s="19" t="str">
         <f>IF($A16="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A16,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D16" s="17" t="str">
+      <c r="D16" s="19" t="str">
         <f>IF($A16="","",SUMIF(Purchases!$A$2:$A$1001,$A16,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A16,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22435,37 +22587,45 @@
         <v/>
       </c>
       <c r="H16" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I16" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K16" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L16" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P16" s="2"/>
+      <c r="Q16" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I16" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J16" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K16" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L16" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="17" t="str">
+      <c r="B17" s="19" t="str">
         <f>IF($A17="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A17,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C17" s="17" t="str">
+      <c r="C17" s="19" t="str">
         <f>IF($A17="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A17,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D17" s="17" t="str">
+      <c r="D17" s="19" t="str">
         <f>IF($A17="","",SUMIF(Purchases!$A$2:$A$1001,$A17,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A17,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22482,37 +22642,45 @@
         <v/>
       </c>
       <c r="H17" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I17" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K17" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L17" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P17" s="2"/>
+      <c r="Q17" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I17" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J17" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K17" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L17" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="17" t="str">
+      <c r="B18" s="19" t="str">
         <f>IF($A18="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A18,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C18" s="17" t="str">
+      <c r="C18" s="19" t="str">
         <f>IF($A18="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A18,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D18" s="17" t="str">
+      <c r="D18" s="19" t="str">
         <f>IF($A18="","",SUMIF(Purchases!$A$2:$A$1001,$A18,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A18,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22529,37 +22697,45 @@
         <v/>
       </c>
       <c r="H18" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I18" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J18" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K18" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L18" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P18" s="2"/>
+      <c r="Q18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I18" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J18" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K18" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L18" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="17" t="str">
+      <c r="B19" s="19" t="str">
         <f>IF($A19="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A19,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C19" s="17" t="str">
+      <c r="C19" s="19" t="str">
         <f>IF($A19="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A19,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D19" s="17" t="str">
+      <c r="D19" s="19" t="str">
         <f>IF($A19="","",SUMIF(Purchases!$A$2:$A$1001,$A19,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A19,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22576,37 +22752,45 @@
         <v/>
       </c>
       <c r="H19" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I19" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J19" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K19" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L19" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P19" s="2"/>
+      <c r="Q19" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A20" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I19" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J19" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K19" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L19" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="17" t="str">
+      <c r="B20" s="19" t="str">
         <f>IF($A20="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A20,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C20" s="17" t="str">
+      <c r="C20" s="19" t="str">
         <f>IF($A20="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A20,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D20" s="17" t="str">
+      <c r="D20" s="19" t="str">
         <f>IF($A20="","",SUMIF(Purchases!$A$2:$A$1001,$A20,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A20,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22623,37 +22807,45 @@
         <v/>
       </c>
       <c r="H20" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I20" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J20" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K20" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L20" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P20" s="2"/>
+      <c r="Q20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I20" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J20" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K20" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L20" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="17" t="str">
+      <c r="B21" s="19" t="str">
         <f>IF($A21="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A21,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C21" s="17" t="str">
+      <c r="C21" s="19" t="str">
         <f>IF($A21="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A21,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D21" s="17" t="str">
+      <c r="D21" s="19" t="str">
         <f>IF($A21="","",SUMIF(Purchases!$A$2:$A$1001,$A21,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A21,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22670,37 +22862,45 @@
         <v/>
       </c>
       <c r="H21" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I21" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J21" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K21" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L21" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P21" s="2"/>
+      <c r="Q21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I21" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J21" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K21" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L21" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="17" t="str">
+      <c r="B22" s="19" t="str">
         <f>IF($A22="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A22,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C22" s="17" t="str">
+      <c r="C22" s="19" t="str">
         <f>IF($A22="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A22,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D22" s="17" t="str">
+      <c r="D22" s="19" t="str">
         <f>IF($A22="","",SUMIF(Purchases!$A$2:$A$1001,$A22,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A22,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22717,37 +22917,45 @@
         <v/>
       </c>
       <c r="H22" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I22" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J22" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K22" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L22" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P22" s="2"/>
+      <c r="Q22" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I22" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J22" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K22" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L22" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="17" t="str">
+      <c r="B23" s="19" t="str">
         <f>IF($A23="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A23,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C23" s="17" t="str">
+      <c r="C23" s="19" t="str">
         <f>IF($A23="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A23,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D23" s="17" t="str">
+      <c r="D23" s="19" t="str">
         <f>IF($A23="","",SUMIF(Purchases!$A$2:$A$1001,$A23,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A23,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22764,37 +22972,45 @@
         <v/>
       </c>
       <c r="H23" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I23" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J23" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K23" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L23" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P23" s="2"/>
+      <c r="Q23" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A24" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I23" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J23" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K23" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L23" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="17" t="str">
+      <c r="B24" s="19" t="str">
         <f>IF($A24="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A24,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C24" s="17" t="str">
+      <c r="C24" s="19" t="str">
         <f>IF($A24="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A24,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D24" s="17" t="str">
+      <c r="D24" s="19" t="str">
         <f>IF($A24="","",SUMIF(Purchases!$A$2:$A$1001,$A24,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A24,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22811,37 +23027,45 @@
         <v/>
       </c>
       <c r="H24" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I24" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J24" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K24" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L24" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P24" s="2"/>
+      <c r="Q24" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A25" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I24" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J24" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K24" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L24" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="17" t="str">
+      <c r="B25" s="19" t="str">
         <f>IF($A25="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A25,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C25" s="17" t="str">
+      <c r="C25" s="19" t="str">
         <f>IF($A25="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A25,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D25" s="17" t="str">
+      <c r="D25" s="19" t="str">
         <f>IF($A25="","",SUMIF(Purchases!$A$2:$A$1001,$A25,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A25,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22858,37 +23082,45 @@
         <v/>
       </c>
       <c r="H25" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I25" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J25" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K25" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L25" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P25" s="2"/>
+      <c r="Q25" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A26" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I25" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J25" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K25" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L25" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="17" t="str">
+      <c r="B26" s="19" t="str">
         <f>IF($A26="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A26,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C26" s="17" t="str">
+      <c r="C26" s="19" t="str">
         <f>IF($A26="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A26,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D26" s="17" t="str">
+      <c r="D26" s="19" t="str">
         <f>IF($A26="","",SUMIF(Purchases!$A$2:$A$1001,$A26,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A26,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22905,37 +23137,45 @@
         <v/>
       </c>
       <c r="H26" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I26" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J26" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K26" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L26" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P26" s="2"/>
+      <c r="Q26" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I26" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J26" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K26" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L26" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="17" t="str">
+      <c r="B27" s="19" t="str">
         <f>IF($A27="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A27,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C27" s="17" t="str">
+      <c r="C27" s="19" t="str">
         <f>IF($A27="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A27,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D27" s="17" t="str">
+      <c r="D27" s="19" t="str">
         <f>IF($A27="","",SUMIF(Purchases!$A$2:$A$1001,$A27,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A27,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22952,37 +23192,45 @@
         <v/>
       </c>
       <c r="H27" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I27" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J27" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K27" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L27" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P27" s="2"/>
+      <c r="Q27" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I27" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J27" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K27" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L27" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="17" t="str">
+      <c r="B28" s="19" t="str">
         <f>IF($A28="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A28,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C28" s="17" t="str">
+      <c r="C28" s="19" t="str">
         <f>IF($A28="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A28,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D28" s="17" t="str">
+      <c r="D28" s="19" t="str">
         <f>IF($A28="","",SUMIF(Purchases!$A$2:$A$1001,$A28,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A28,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -22999,37 +23247,45 @@
         <v/>
       </c>
       <c r="H28" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I28" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J28" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K28" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L28" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P28" s="2"/>
+      <c r="Q28" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A29" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I28" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J28" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K28" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L28" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="17" t="str">
+      <c r="B29" s="19" t="str">
         <f>IF($A29="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A29,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C29" s="17" t="str">
+      <c r="C29" s="19" t="str">
         <f>IF($A29="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A29,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D29" s="17" t="str">
+      <c r="D29" s="19" t="str">
         <f>IF($A29="","",SUMIF(Purchases!$A$2:$A$1001,$A29,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A29,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23046,37 +23302,45 @@
         <v/>
       </c>
       <c r="H29" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I29" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J29" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K29" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L29" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P29" s="2"/>
+      <c r="Q29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A30" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I29" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J29" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K29" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L29" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="17" t="str">
+      <c r="B30" s="19" t="str">
         <f>IF($A30="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A30,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C30" s="17" t="str">
+      <c r="C30" s="19" t="str">
         <f>IF($A30="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A30,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D30" s="17" t="str">
+      <c r="D30" s="19" t="str">
         <f>IF($A30="","",SUMIF(Purchases!$A$2:$A$1001,$A30,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A30,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23093,37 +23357,45 @@
         <v/>
       </c>
       <c r="H30" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I30" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J30" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K30" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L30" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P30" s="2"/>
+      <c r="Q30" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I30" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K30" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L30" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="17" t="str">
+      <c r="B31" s="19" t="str">
         <f>IF($A31="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A31,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C31" s="17" t="str">
+      <c r="C31" s="19" t="str">
         <f>IF($A31="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A31,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D31" s="17" t="str">
+      <c r="D31" s="19" t="str">
         <f>IF($A31="","",SUMIF(Purchases!$A$2:$A$1001,$A31,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A31,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23140,37 +23412,45 @@
         <v/>
       </c>
       <c r="H31" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I31" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J31" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K31" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L31" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P31" s="2"/>
+      <c r="Q31" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I31" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J31" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K31" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L31" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="17" t="str">
+      <c r="B32" s="19" t="str">
         <f>IF($A32="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A32,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C32" s="17" t="str">
+      <c r="C32" s="19" t="str">
         <f>IF($A32="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A32,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D32" s="17" t="str">
+      <c r="D32" s="19" t="str">
         <f>IF($A32="","",SUMIF(Purchases!$A$2:$A$1001,$A32,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A32,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23187,37 +23467,45 @@
         <v/>
       </c>
       <c r="H32" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I32" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J32" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K32" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L32" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P32" s="2"/>
+      <c r="Q32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A33" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I32" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K32" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L32" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="17" t="str">
+      <c r="B33" s="19" t="str">
         <f>IF($A33="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A33,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C33" s="17" t="str">
+      <c r="C33" s="19" t="str">
         <f>IF($A33="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A33,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D33" s="17" t="str">
+      <c r="D33" s="19" t="str">
         <f>IF($A33="","",SUMIF(Purchases!$A$2:$A$1001,$A33,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A33,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23234,37 +23522,45 @@
         <v/>
       </c>
       <c r="H33" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I33" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J33" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K33" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L33" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P33" s="2"/>
+      <c r="Q33" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A34" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I33" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K33" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L33" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="17" t="str">
+      <c r="B34" s="19" t="str">
         <f>IF($A34="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A34,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C34" s="17" t="str">
+      <c r="C34" s="19" t="str">
         <f>IF($A34="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A34,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D34" s="17" t="str">
+      <c r="D34" s="19" t="str">
         <f>IF($A34="","",SUMIF(Purchases!$A$2:$A$1001,$A34,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A34,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23281,37 +23577,45 @@
         <v/>
       </c>
       <c r="H34" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I34" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J34" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K34" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L34" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P34" s="2"/>
+      <c r="Q34" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I34" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K34" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L34" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="17" t="str">
+      <c r="B35" s="19" t="str">
         <f>IF($A35="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A35,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C35" s="17" t="str">
+      <c r="C35" s="19" t="str">
         <f>IF($A35="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A35,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D35" s="17" t="str">
+      <c r="D35" s="19" t="str">
         <f>IF($A35="","",SUMIF(Purchases!$A$2:$A$1001,$A35,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A35,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23328,37 +23632,45 @@
         <v/>
       </c>
       <c r="H35" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I35" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J35" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K35" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L35" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P35" s="2"/>
+      <c r="Q35" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I35" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K35" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L35" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-      <c r="B36" s="17" t="str">
+      <c r="B36" s="19" t="str">
         <f>IF($A36="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A36,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C36" s="17" t="str">
+      <c r="C36" s="19" t="str">
         <f>IF($A36="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A36,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D36" s="17" t="str">
+      <c r="D36" s="19" t="str">
         <f>IF($A36="","",SUMIF(Purchases!$A$2:$A$1001,$A36,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A36,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23375,37 +23687,45 @@
         <v/>
       </c>
       <c r="H36" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I36" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J36" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K36" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L36" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P36" s="2"/>
+      <c r="Q36" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A37" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I36" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J36" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K36" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L36" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-      <c r="B37" s="17" t="str">
+      <c r="B37" s="19" t="str">
         <f>IF($A37="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A37,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C37" s="17" t="str">
+      <c r="C37" s="19" t="str">
         <f>IF($A37="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A37,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D37" s="17" t="str">
+      <c r="D37" s="19" t="str">
         <f>IF($A37="","",SUMIF(Purchases!$A$2:$A$1001,$A37,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A37,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23422,37 +23742,45 @@
         <v/>
       </c>
       <c r="H37" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I37" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J37" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K37" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L37" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P37" s="2"/>
+      <c r="Q37" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A38" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I37" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J37" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K37" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L37" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="17" t="str">
+      <c r="B38" s="19" t="str">
         <f>IF($A38="","",SUMIFS(Purchases!$C$2:$C$1001,Purchases!$A$2:$A$1001,$A38,Purchases!$B$2:$B$1001,"&gt;="&amp;$B$5,Purchases!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="C38" s="17" t="str">
+      <c r="C38" s="19" t="str">
         <f>IF($A38="","",SUMIFS(Sales!$C$2:$C$1001,Sales!$A$2:$A$1001,$A38,Sales!$B$2:$B$1001,"&gt;="&amp;$B$5,Sales!$B$2:$B$1001,"&lt;="&amp;$D$5))</f>
         <v/>
       </c>
-      <c r="D38" s="17" t="str">
+      <c r="D38" s="19" t="str">
         <f>IF($A38="","",SUMIF(Purchases!$A$2:$A$1001,$A38,Purchases!$C$2:$C$1001)-SUMIF(Sales!$A$2:$A$1001,$A38,Sales!$C$2:$C$1001))</f>
         <v/>
       </c>
@@ -23469,23 +23797,34 @@
         <v/>
       </c>
       <c r="H38" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I38" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J38" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K38" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L38" s="19" t="str">
+      <c r="K38" s="20" t="str">
         <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L38" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P38" s="2"/>
+      <c r="Q38" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q39" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -23505,13 +23844,16 @@
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" sqref="B3" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$N$3:$N$11</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Enter a valid date." sqref="B4 D4" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>36526</formula1>
     </dataValidation>
+    <dataValidation type="list" sqref="B6" xr:uid="{00000000-0002-0000-0200-000002000000}">
+      <formula1>OFFSET($Q$9,0,0,COUNTA($P$9:$P$38)+1,1)</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
